--- a/artfynd/A 59019-2024 artfynd.xlsx
+++ b/artfynd/A 59019-2024 artfynd.xlsx
@@ -3267,7 +3267,7 @@
         <v>136162944</v>
       </c>
       <c r="B27" t="n">
-        <v>57844</v>
+        <v>57846</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
